--- a/content/tz-znachenie-cvetov-v-kitae.xlsx
+++ b/content/tz-znachenie-cvetov-v-kitae.xlsx
@@ -14,6 +14,8 @@
     <sheet name="Мета-теги" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="JSON-LD" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="sameAs — где брать" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Перелинковка" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Проверки перед сдачей" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +38,7 @@
       <color rgb="002C2420"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E3F6E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7E6EB"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -89,6 +96,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -456,11 +466,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,7 +493,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ТЗ на статью «Значение цветов в Китае» (раздел «Культура Китая»). Информационно-культурологический текст.</t>
+          <t>ТЗ на расширение ОПУБЛИКОВАННОЙ статьи /article/znachenie-cvetov-v-kitae под бриф «значение цвета в китайской культуре» (раздел «Культура Китая»).</t>
         </is>
       </c>
     </row>
@@ -502,48 +512,96 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Отстройка</t>
+          <t>ВАЖНО: почему не новая статья</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Не просто «красный = удача», а смыслы + происхождение (у-син) + практические «можно/нельзя» (зелёная шляпа, красные чернила, белая упаковка).</t>
+          <t>Бриф просил отдельную статью, но запрос «символика цвета в китайской культуре» уже стоял в keywords этой опубликованной страницы, а «значение цвета в Китае» и «что означают цвета в Китае» — те же слова в другом порядке. Две наши страницы конкурировали бы за один интент. Поэтому статья расширена под новый бриф: новые title, description, keywords, H1, четыре новых H2, три новых вопроса в FAQ.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Картинки</t>
+          <t>Что реально добавлено</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Hero «颜色» с 5 цветными плашками + инфографика «Цвета Китая и их смыслы» — в СЕРЕДИНУ, в РЕАЛЬНЫХ цветах.</t>
+          <t>青 (qīng) — в старом тексте 0 упоминаний. Голубой — было одно слово «синий» вскользь. «Какой цвет любят китайцы» — 0 упоминаний. Традиционные цвета 正色/间色 — была только таблица у-син.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Оформление</t>
+          <t>Правило на будущее</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Блок «Из личного опыта» (кейс с зелёными кепками) — в СЕРЕДИНЕ. Блок «Коротко» — правило .tldr&gt;b.</t>
+          <t>Если бриф повторяет keywords уже опубликованной статьи — расширяем её, а не создаём вторую. Отдельная статья оправдана, когда у подтемы есть свой самостоятельный запрос: так сделаны «жёлтый цвет» и «фиолетовый цвет».</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>Отстройка</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Пять вещей, которых нет в выдаче: (1) деление 正色 / 间色 и статус за ним; (2) 赤 против 红 — в пятёрку входит не то слово, которым сегодня называют красный; (3) 青 — зелёный, синий и чёрный в одном знаке; (4) честный ответ про голубой: отдельного цвета нет, есть 浅蓝; (5) разведение «любимого цвета» и «главного символа».</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Картинки</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Hero «颜色 · пять правильных цветов» + инфографика «Цвет в Китае — это система» — в СЕРЕДИНУ (46 % текста). Обе ПЕРЕРИСОВАНЫ, нужно перезалить в Tilda и заменить URL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Оформление</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Иероглифы в таблицах — .han-cell, знаки в тексте — .han-big, цветные плашки — .sw. В CSS этой статьи добавлены правила .han-cell и .sw, которых раньше не было. «Из личного опыта» — в СЕРЕДИНЕ (39 %). Блок «Коротко» — .tldr&gt;b.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>Язык</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Живой, простой язык.</t>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Живой, простой язык, без «воды». Кавычки — «ёлочки», тире по русской пунктуации.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Статья опубликована. После правок блок нужно ПЕРЕВСТАВИТЬ в Tilda и перезалить обе картинки.</t>
         </is>
       </c>
     </row>
@@ -558,18 +616,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -595,26 +652,21 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
           <t>Объём
 (знаков от)</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Тип / Schema @type</t>
+        </is>
+      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Тип / Schema @type</t>
+          <t>URL (ЧПУ)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>URL (ЧПУ)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Интент</t>
         </is>
@@ -623,47 +675,42 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Значение цветов в Китае: краткий путеводитель по символике основных оттенков</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>значение цветов в Китае; зелёный цвет в Китае символизирует; что обозначают цвета в Китае; символизм цветов в Китае; символика цвета в китайской культуре</t>
+          <t>значение цвета в Китае; что означают цвета в Китае; цвет цин в Китае; какой цвет любят китайцы; символика цвета в Китае; традиционные китайские цвета; значение цвета в китайской культуре; какой цвет любят в Китае; что значит голубой цвет в Китае</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>颜色; 五行 у-син; 红包; 戴绿帽子; 白事; 黄色; красный; траур; император</t>
+          <t>颜色; 五行; 正色; 间色; 青; 赤; 黄; 白; 黑; 红; 绿; 蓝; 紫; 碧; 浅蓝; 天蓝; 湖蓝; 青草; 青天; 青丝; 青花瓷; 青山; 青年; 青春; 青出于蓝; 红包; 白事; 黑市; 戴绿帽子; 黄色</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Почему цвет — это язык · Красный 红 · Жёлтый и золотой 黄 · Зелёный 绿 · Из личного опыта · Белый и чёрный 白·黑 · Как пользоваться цветом · FAQ</t>
+          <t>Почему цвет в Китае — это язык · Пять «правильных» цветов и все остальные (НОВЫЙ) · Красный 红 · Жёлтый и золотой 黄 · Зелёный 绿 · Из личного опыта · Белый и чёрный 白·黑 · инфографика · 青 (qīng) — цвет, которого нет в русском (НОВЫЙ) · Синий 蓝 — и куда делся голубой (НОВЫЙ) · Какой цвет любят китайцы (НОВЫЙ) · Как пользоваться цветом правильно · FAQ (8 вопросов)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>у-син стихия/цвет · красные чернила · 黄色 · зелёная шляпа · белое дело</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>11000</t>
+          <t>BlogPosting + FAQPage + Person + EducationalOrganization + BreadcrumbList</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>BlogPosting + FAQPage + Person + EducationalOrganization + BreadcrumbList</t>
+          <t>/article/znachenie-cvetov-v-kitae (НЕ меняется)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>/article/znachenie-cvetov-v-kitae</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Информационно-культурологический</t>
+          <t>Информационно-культурологический, хаб раздела: целостная система, а не набор примет</t>
         </is>
       </c>
     </row>
@@ -678,17 +725,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -714,7 +761,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Источник</t>
+          <t>Область</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -736,7 +783,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -751,12 +798,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>у-син (пять стихий)</t>
+          <t>у-син, пять стихий</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>философия</t>
+          <t>культура</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -766,123 +813,123 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>«Почему язык»</t>
+          <t>«Почему язык» + инфографика</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>отстройка</t>
+          <t>факт</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>Пять «правильных» цветов 正色</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>символизирует</t>
+          <t>это</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>удачу, праздник, счастье</t>
+          <t>青, 赤, 黄, 白, 黑</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>культура</t>
+          <t>система</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ОБЯЗАТ</t>
+          <t>ОТСТРОЙКА</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>«Красный» + FAQ</t>
+          <t>Таблица 正色 + hero + инфографика</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>факт</t>
+          <t>отстройка</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Красный</t>
+          <t>Смешанные цвета</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>отпугивает</t>
+          <t>называются</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>злых духов (легенда о Нянь)</t>
+          <t>间色 (jiānsè)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>легенда</t>
+          <t>система</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>ОБЯЗАТ</t>
+          <t>ОТСТРОЙКА</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>«Красный»</t>
+          <t>Абзац + инфографика</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>факт</t>
+          <t>отстройка</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Красные чернила</t>
+          <t>正色</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>нельзя писать</t>
+          <t>ценились выше</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>имена людей</t>
+          <t>чем 间色</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>примета</t>
+          <t>статус</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -892,7 +939,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Абзац после таблицы</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -904,69 +951,69 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Жёлтый</t>
+          <t>赤 (chì)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>был цветом</t>
+          <t>это</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>императора (Мин, Цин)</t>
+          <t>«правильный» красный, а не 红</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>история</t>
+          <t>лексика</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>ОБЯЗАТ</t>
+          <t>ОТСТРОЙКА</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>«Жёлтый»</t>
+          <t>Абзац + инфографика</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>факт</t>
+          <t>отстройка</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>黄色</t>
+          <t>红 (hóng)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>означает</t>
+          <t>раньше означало</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>непристойное содержание</t>
+          <t>светло-красный, считалось смешанным</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>язык</t>
+          <t>лексика</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -976,7 +1023,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Абзац + инфографика</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -988,22 +1035,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Зелёный</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>означает</t>
+          <t>символизирует</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>рост, здоровье, весну</t>
+          <t>удачу, праздник, счастье</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1018,7 +1065,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>«Зелёный»</t>
+          <t>«Красный» + TL;DR + FAQ</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1030,126 +1077,924 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Зелёная шляпа (戴绿帽子)</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>означает</t>
+          <t>отпугивает</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>измену жены</t>
+          <t>злых духов, легенда о Нянь</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>идиома</t>
+          <t>предание</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>ОТСТРОЙКА</t>
+          <t>ОБЯЗАТ</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>ks-quote + FAQ</t>
+          <t>«Красный»</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>отстройка</t>
+          <t>факт</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Белый</t>
+          <t>Красными чернилами</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>связан с</t>
+          <t>нельзя писать</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>трауром, похоронами (白事)</t>
+          <t>имена людей</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>культура</t>
+          <t>табу</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>ОБЯЗАТ</t>
+          <t>ОТСТРОЙКА</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>«Белый и чёрный» + FAQ</t>
+          <t>note + FAQ + инфографика</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>факт</t>
+          <t>отстройка</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>Жёлтый</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>был цветом</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>императора при Мин и Цин</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>история</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>ОБЯЗАТ</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>«Жёлтый» + FAQ</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>факт</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>黄色</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>означает</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>непристойное содержание</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>современность</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>note + FAQ</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>отстройка</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Зелёный</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>означает</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>рост, здоровье, весну</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>культура</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>ОБЯЗАТ</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>«Зелёный»</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>факт</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>戴绿帽子</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>означает</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>измену жены</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>идиома</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>ks-quote + FAQ + инфографика</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>отстройка</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Белый</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>связан с</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>трауром, похороны — 白事</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>культура</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>ОБЯЗАТ</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>«Белый и чёрный» + FAQ</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>факт</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>Чёрный</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>означает</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>серьёзность; также незаконное (黑市)</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>серьёзность; также незаконное — 黑市</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>культура</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>ОБЯЗАТ</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>«Белый и чёрный»</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>факт</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>青 (qīng)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>покрывает</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>зелёный, синий и чёрный сразу</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>лексика</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Таблица + инфографика + FAQ</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>отстройка</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>青草</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>это</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>зелёная трава</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>лексика</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Таблица 青 + инфографика</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>отстройка</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>青天</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>это</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>синее небо</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>лексика</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Таблица 青 + инфографика</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>отстройка</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>青丝</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>это</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>чёрные волосы, поэтическое</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>лексика</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Таблица 青 + инфографика</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>отстройка</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>青花瓷</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>это</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>сине-белый фарфор, но в названии 青</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>лексика</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Таблица 青 + ks-quote</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>отстройка</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>青</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>называет</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>область смысла, а не оттенок</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>методика</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Абзац + инфографика + FAQ</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>отстройка</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>青 по у-син</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>это</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>восток, дерево, весна — отсюда молодость</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>система</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Абзац: 青年, 青春</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>отстройка</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>青出于蓝</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>значит</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>ученик превзошёл учителя</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>идиома</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Абзац + источники</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>отстройка</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>蓝 (lán)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>изначально</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>название растения индиго</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>этимология</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>«Синий»</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>отстройка</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Голубой</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>не выделен</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>в китайском отдельным цветом</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>лексика</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>«Синий» + FAQ + инфографика</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>отстройка</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Голубой</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>передаётся как</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>浅蓝, 天蓝, 湖蓝</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>лексика</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>«Синий» + FAQ</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>отстройка</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Синий</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>в трауре</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>входит в гамму с белым и чёрным</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>этикет</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>«Синий» + FAQ</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>отстройка</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Любимый цвет китайцев</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>это</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>красный, затем золотой</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>практика</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>ОБЯЗАТ</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>«Какой цвет любят» + FAQ</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>факт</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Красный</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>любят как</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>цвет повода, а не гардероба</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>практика</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>ОТСТРОЙКА</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>«Какой цвет любят» + FAQ</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>отстройка</t>
         </is>
       </c>
     </row>
@@ -1164,12 +2009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="96" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1192,7 +2037,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1202,141 +2047,226 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>В Китае цвет — это язык. За каждым оттенком стоят устойчивые ассоциации: красный зовёт удачу, белый связан с трауром, жёлтый когда-то принадлежал императору.</t>
+          <t>В Китае цвет — это не украшение, а язык. За каждым оттенком стоят устойчивые смыслы, собранные в систему: пять стихий, пять сторон света, пять «правильных» цветов. Красный зовёт удачу, белый связан с трауром, жёлтый веками принадлежал одному человеку в стране, а цвет 青 (qīng) вообще не переводится на русский одним словом. Ниже — не список примет, а связная картина.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TL;DR</t>
+          <t>TL;DR «Коротко»</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Красный — праздник и удача; жёлтый и золотой — власть; зелёный — рост, но «зелёная шляпа» = измена; белый и чёрный — траур и серьёзность. Дарите в красном и золотом, избегайте белой упаковки, не пишите имена красным.</t>
+          <t>Система идёт от пяти стихий: цвет привязан к стороне света и времени года. Пять «правильных» цветов — 青, 赤, 黄, 白, 黑; всё остальное считалось смешанным. Красный — праздник и удача. Жёлтый и золотой — власть и богатство. Зелёный — рост, но «зелёная шляпа» — обидный намёк. Белый и чёрный — траур и серьёзность. 青 (qīng) — цвет без русского аналога.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Цитата</t>
+          <t>ks-quote 1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>戴绿帽子 (dài lǜ màozi) — «носить зелёную шляпу» — значит, что мужчине изменяет жена.</t>
+          <t>戴绿帽子 (dài lǜ màozi) — «носить зелёную шляпу» — значит, что мужчине изменяет жена. // cite: идиома, которую важно знать до похода в гости</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>FAQ 1</t>
+          <t>ks-quote 2 (новая)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Красный? — Праздник, удача, счастье; свадьбы, Новый год, конверты 红包; отпугивает злых духов.</t>
+          <t>青花瓷 (qīnghuācí) — знаменитый бело-синий фарфор. Цвет на нём кобальтовый, синий, но в названии стоит 青, а не 蓝. // cite: хороший пример того, как старое слово держится в именах вещей</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FAQ 2</t>
+          <t>Из личного опыта</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Зелёный? — Рост, здоровье, весна; но «зелёная шляпа» 戴绿帽子 = измена, нельзя дарить зелёный головной убор.</t>
+          <t>Кейс с зелёными кепками для китайских партнёров — оставлен без изменений, стоит в СЕРЕДИНЕ (39 % текста).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FAQ 3</t>
+          <t>FAQ 1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Почему белый — траур? — Похороны называют «белым делом» 白事; белую упаковку/одежду на праздник не используют.</t>
+          <t>Что символизирует красный цвет в Китае? — Праздник, удача, счастье; свадьбы, Новый год, конверты 红包; отпугивает злых духов.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>FAQ 4</t>
+          <t>FAQ 2</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Императорский цвет? — Жёлтый (золотой), был закреплён за императором; 黄色 = ещё и «непристойное».</t>
+          <t>Что символизирует зелёный цвет в Китае? — Рост, здоровье, весна; но «зелёная шляпа» 戴绿帽子 = измена.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FAQ 5</t>
+          <t>FAQ 3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Красные чернила для имени? — Нет: так писали имена умерших/приговорённых, плохая примета.</t>
+          <t>Почему в Китае белый цвет связан с трауром? — Похороны называют «белым делом» 白事.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>FAQ 4</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Какой цвет в Китае считается императорским? — Жёлтый и золотой; 黄色 = ещё и «непристойное».</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>FAQ 5</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Можно ли писать имя человека красными чернилами? — Нет, так писали имена умерших и приговорённых.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>FAQ 6 (новый)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Что за цвет 青 (qīng) и почему его не переводят одним словом? — Сразу зелёный, синий и тёмный: 青草, 青天, 青丝. Называет область, а не оттенок; переводить нужно по предмету.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>FAQ 7 (новый)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Что значит голубой цвет в Китае? — Отдельного слова нет: есть 蓝 «синий», голубой — это 浅蓝 или 天蓝. Значения спокойные, плохих примет нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>FAQ 8 (новый)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Какой цвет любят китайцы? — Красный вне конкуренции, затем золотой. Но как цвет повода: в обычной одежде чаще чёрный, белый и серый.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>Подпись</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>红红火火！ (hónghóng huǒhuǒ! — «пусть жизнь пылает удачей!»)</t>
         </is>
@@ -1353,13 +2283,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="84" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1387,7 +2317,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1397,7 +2327,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Значение цветов в Китае: символика красного, зелёного, белого</t>
+          <t>Значение цвета в китайской культуре: система смыслов от красного до белого</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1409,7 +2339,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1419,7 +2349,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Значение цветов в Китае: что символизируют красный, жёлтый, зелёный, белый и чёрный в китайской культуре, откуда идут эти смыслы и в каких случаях цвет лучше не использовать — например, почему нельзя дарить мужчине зелёную шляпу.</t>
+          <t>Цвета в Китае — это не эстетика, а язык символов, связанный со стихиями, сторонами света и обрядами. Разбираем, почему красный означает радость, белый связан с трауром, а 青 (qīng) вообще не имеет точного аналога в русском. Целостная картина, а не разрозненные факты.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1431,51 +2361,51 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Значение цветов в Китае: краткий путеводитель по символике основных оттенков</t>
+          <t>значение цвета в Китае, что означают цвета в Китае, цвет цин в Китае, какой цвет любят китайцы, символика цвета в Китае, традиционные китайские цвета, значение цвета в китайской культуре, какой цвет любят в Китае, что значит голубой цвет в Китае, значение цветов в Китае, зеленый цвет в Китае символизирует, что обозначают цвета в Китае</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Одна на страницу</t>
+          <t>Новые КС брифа + сохранены старые</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>og:title</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Значение цветов в Китае: символика красного, зелёного, белого</t>
+          <t>Значение цвета в китайской культуре: система смыслов от красного до белого</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Дублирует title</t>
+          <t>Одна на страницу</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1490,29 +2420,73 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ЧПУ, без параметров</t>
+          <t>НЕ меняется — расширяем существующий URL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>og:title</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре: система смыслов</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Короткий вариант для соцсетей</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>article:modified_time</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Обновлено при расширении</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Значение цвета в китайской культуре</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>og:image</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Брендовая карточка «颜色» с 5 цветными плашками (alt: «Значение цветов в Китае»)</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1200×630</t>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Брендовая карточка «颜色 · пять правильных цветов»</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1200×630, ПЕРЕРИСОВАНА</t>
         </is>
       </c>
     </row>
@@ -1530,10 +2504,10 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1561,7 +2535,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Цвета Китая</t>
+          <t>Значение цвета в китайской культуре</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1571,12 +2545,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>См. готовый блок &lt;script type="application/ld+json"&gt; в файле статьи</t>
+          <t>См. готовый блок в файле статьи</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>about → «Символика цвета» (sameAs: У-син, Красный цвет); FAQPage дословно совпадает с видимым FAQ</t>
+          <t>about → «Символика цвета в китайской культуре»; FAQPage — 8 вопросов, дословно совпадает с видимым FAQ (проверено скриптом); dateModified = 2026-08-25; крошка переименована</t>
         </is>
       </c>
     </row>
@@ -1591,14 +2565,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1651,7 +2625,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Основа символики цвета</t>
+          <t>about/sameAs</t>
         </is>
       </c>
     </row>
@@ -1678,34 +2652,512 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Символика красного</t>
+          <t>about/sameAs</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Цин (цвет)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Thing</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Википедия «Цин (цвет)»</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://ru.wikipedia.org/wiki/Цин_(цвет)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>about/sameAs — ДОБАВЛЕН при расширении</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Китайский Новый год</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Thing</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Википедия</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://ru.wikipedia.org/wiki/Китайский_Новый_год</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>mentions</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>Юлия Горяина</t>
         </is>
       </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Внутренний узел /about</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>https://kitai-school.ru/about</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Автор публикации</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Kitai School</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>EducationalOrganization</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Соцсети школы</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>https://vk.com/kitai_school; https://telegram.me/kitai_school</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Издатель</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Куда ведёт</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Адрес</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Откуда в тексте</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Китайский этикет общения</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>/article/kitayskiy-tiket-obscheniya-uvajenie-k-starshim-ierarhiya-i-ponyatie-lica</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>«Как пользоваться цветом» + финальный абзац</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>реальный URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Весна по-китайски</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>/article/vesna-po-kitayski--ieroglif--i-umenie-chuvstvovat-kontekst</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Раздел «Красный»</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>реальный URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Национальное животное Китая</t>
+        </is>
+      </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
+          <t>/article/nacionalnoe-jivotnoe-kitaya-bolshaya-panda</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Внутренний узел /about</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>https://kitai-school.ru/about</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Автор публикации</t>
+          <t>Финальный абзац</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>реальный URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Жёлтый цвет в Китае</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>/article/znachenie-zheltogo-cveta-v-kitae</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>note в разделе «Жёлтый»</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>адрес предположительный</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Фиолетовый цвет в Китае</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>/article/znachenie-fioletovogo-cveta-v-kitae</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>note в разделе «Пять правильных цветов» + note в «Жёлтом»</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>адрес предположительный</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Цвета на китайском с транскрипцией</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>/article/cveta-na-kitajskom</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>note в разделе «青»</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>адрес предположительный — НОВАЯ ссылка</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Что проверяем</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Как</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Результат</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Липкий сайдбар на десктопе</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Playwright, getComputedStyle(#ks-side).top</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>top = 90px — ОК</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Мобильная вёрстка</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Playwright, viewport 390, document.body.scrollWidth</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>docWidth = 390, горизонтального скролла нет — ОК</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Баланс тегов div</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>rebuild.py</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>30 / 30 — ОК</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Футер «Для записи»</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Поиск по файлу</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0 вхождений — ОК</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Валидность JSON-LD</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>json.loads</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5 узлов в @graph — ОК</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>FAQPage = видимый FAQ</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Сверка вопрос-в-вопрос</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8 / 8, дословно — ОК</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Лимит блока T123</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>len() готового блока</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>45 108 знаков из 50 000 — ОК</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Прямые кавычки в тексте</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Регулярка по видимому тексту</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0 — везде «ёлочки»</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Двойной дефис и дефис в роли тире</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Регулярка</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0 / 0 — ОК</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Обе картинки прочитаны глазами</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Просмотр PNG</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Да: в hero правился налёт заголовка на карточку 青, в инфографике — пустая нижняя треть и конфликт классов</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Инфографика и «Из личного опыта» в середине</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Замер позиции в тексте</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>39 % и 46 % — ОК</t>
         </is>
       </c>
     </row>
